--- a/data/raw/김포 26년/항공통계상세조회(노선) (1).xlsx
+++ b/data/raw/김포 26년/항공통계상세조회(노선) (1).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>10985</t>
-  </si>
-  <si>
-    <t>1983009</t>
-  </si>
-  <si>
-    <t>16514</t>
+    <t>5496</t>
+  </si>
+  <si>
+    <t>990061</t>
+  </si>
+  <si>
+    <t>7582</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,181 +53,169 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>558</t>
-  </si>
-  <si>
-    <t>102764</t>
-  </si>
-  <si>
-    <t>1028</t>
+    <t>279</t>
+  </si>
+  <si>
+    <t>52578</t>
+  </si>
+  <si>
+    <t>510</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>6278</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>719</t>
+  </si>
+  <si>
+    <t>104952</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>나고야(NGO)</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>9724</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>5549</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>85255</t>
+  </si>
+  <si>
+    <t>1625</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>14826</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>6368</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>10723</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>9810</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>10266</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3364</t>
+  </si>
+  <si>
+    <t>638232</t>
+  </si>
+  <si>
+    <t>3988</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>9056</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>1995</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
+  </si>
+  <si>
     <t>124</t>
   </si>
   <si>
-    <t>13140</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1437</t>
-  </si>
-  <si>
-    <t>210788</t>
-  </si>
-  <si>
-    <t>772</t>
-  </si>
-  <si>
-    <t>나고야(NGO)</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>19169</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>11261</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>744</t>
-  </si>
-  <si>
-    <t>161965</t>
-  </si>
-  <si>
-    <t>2598</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>29540</t>
-  </si>
-  <si>
-    <t>373</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>13334</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>21288</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>20583</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>21013</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>6721</t>
-  </si>
-  <si>
-    <t>1286903</t>
-  </si>
-  <si>
-    <t>9868</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>18309</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>타이페이(TPE)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>4080</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>48694</t>
-  </si>
-  <si>
-    <t>805</t>
+    <t>24449</t>
+  </si>
+  <si>
+    <t>318</t>
   </si>
 </sst>
 </file>
@@ -278,7 +266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="30"/>
   <sheetData>
     <row r="1">
@@ -592,13 +580,13 @@
         <v>61</v>
       </c>
       <c r="D16" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="E16" t="s" s="0">
+      <c r="F16" t="s" s="0">
         <v>63</v>
-      </c>
-      <c r="F16" t="s" s="0">
-        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -609,36 +597,16 @@
         <v>11</v>
       </c>
       <c r="C17" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="D17" t="s" s="0">
         <v>65</v>
-      </c>
-      <c r="D17" t="s" s="0">
-        <v>29</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>66</v>
       </c>
       <c r="F17" t="s" s="0">
         <v>67</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n" s="0">
-        <v>16.0</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>69</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="F18" t="s" s="0">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
